--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -585,6 +585,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1065,7 +1076,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,25,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*Cọc khoan nhồi*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 25, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Cọc khoan nhồi*")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n">
@@ -1094,8 +1105,8 @@
         <f>F6*3.853</f>
         <v/>
       </c>
-      <c r="L6" s="11">
-        <f>(J6/I6)*100</f>
+      <c r="L6" s="99">
+        <f>IF(I6=0, 0, (J6/I6)*100)</f>
         <v/>
       </c>
     </row>
@@ -1114,7 +1125,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đai tăng cường cọc*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Cọc khoan nhồi*")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n">
@@ -1143,8 +1154,8 @@
         <f>F7*1.578</f>
         <v/>
       </c>
-      <c r="L7" s="11">
-        <f>(J7/I7)*100</f>
+      <c r="L7" s="99">
+        <f>IF(I7=0, 0, (J7/I7)*100)</f>
         <v/>
       </c>
     </row>
@@ -1163,7 +1174,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,10,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đai xoắn*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 10, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Cọc khoan nhồi*")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n">
@@ -1192,8 +1203,8 @@
         <f>F8*0.617</f>
         <v/>
       </c>
-      <c r="L8" s="11">
-        <f>(J8/I8)*100</f>
+      <c r="L8" s="99">
+        <f>IF(I8=0, 0, (J8/I8)*100)</f>
         <v/>
       </c>
     </row>
@@ -1212,7 +1223,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,32,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đáy bệ móng*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 32, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Trụ*") + COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 32, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Mố*")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n">
@@ -1241,8 +1252,8 @@
         <f>F9*6.313</f>
         <v/>
       </c>
-      <c r="L9" s="11">
-        <f>(J9/I9)*100</f>
+      <c r="L9" s="99">
+        <f>IF(I9=0, 0, (J9/I9)*100)</f>
         <v/>
       </c>
     </row>
@@ -1261,7 +1272,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,20,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*phân bố bệ*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 20, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Trụ*") + COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 20, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Mố*")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n">
@@ -1290,8 +1301,8 @@
         <f>F10*2.466</f>
         <v/>
       </c>
-      <c r="L10" s="11">
-        <f>(J10/I10)*100</f>
+      <c r="L10" s="99">
+        <f>IF(I10=0, 0, (J10/I10)*100)</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1321,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,28,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thân mố*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 28, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Mố*")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n">
@@ -1339,8 +1350,8 @@
         <f>F11*4.834</f>
         <v/>
       </c>
-      <c r="L11" s="11">
-        <f>(J11/I11)*100</f>
+      <c r="L11" s="99">
+        <f>IF(I11=0, 0, (J11/I11)*100)</f>
         <v/>
       </c>
     </row>
@@ -1359,7 +1370,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,32,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thân đặc trụ*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 32, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Trụ*")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n">
@@ -1388,8 +1399,8 @@
         <f>F12*6.313</f>
         <v/>
       </c>
-      <c r="L12" s="11">
-        <f>(J12/I12)*100</f>
+      <c r="L12" s="99">
+        <f>IF(I12=0, 0, (J12/I12)*100)</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1419,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,28,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*xà mũ trụ*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 28, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Trụ*")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n">
@@ -1437,8 +1448,8 @@
         <f>F13*4.834</f>
         <v/>
       </c>
-      <c r="L13" s="11">
-        <f>(J13/I13)*100</f>
+      <c r="L13" s="99">
+        <f>IF(I13=0, 0, (J13/I13)*100)</f>
         <v/>
       </c>
     </row>
@@ -1457,7 +1468,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thường dầm Super-T*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Super-T*")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n">
@@ -1486,8 +1497,8 @@
         <f>F14*1.578</f>
         <v/>
       </c>
-      <c r="L14" s="11">
-        <f>(J14/I14)*100</f>
+      <c r="L14" s="99">
+        <f>IF(I14=0, 0, (J14/I14)*100)</f>
         <v/>
       </c>
     </row>
@@ -1506,7 +1517,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,14,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thường dầm Super-T*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 14, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Super-T*")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n">
@@ -1535,8 +1546,8 @@
         <f>F15*1.208</f>
         <v/>
       </c>
-      <c r="L15" s="11">
-        <f>(J15/I15)*100</f>
+      <c r="L15" s="99">
+        <f>IF(I15=0, 0, (J15/I15)*100)</f>
         <v/>
       </c>
     </row>
@@ -1555,7 +1566,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*dầm ngang*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Dầm ngang*")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n">
@@ -1584,8 +1595,8 @@
         <f>F16*1.578</f>
         <v/>
       </c>
-      <c r="L16" s="11">
-        <f>(J16/I16)*100</f>
+      <c r="L16" s="99">
+        <f>IF(I16=0, 0, (J16/I16)*100)</f>
         <v/>
       </c>
     </row>
@@ -1604,7 +1615,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản mặt cầu*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Bản*")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n">
@@ -1633,8 +1644,8 @@
         <f>F17*1.578</f>
         <v/>
       </c>
-      <c r="L17" s="11">
-        <f>(J17/I17)*100</f>
+      <c r="L17" s="99">
+        <f>IF(I17=0, 0, (J17/I17)*100)</f>
         <v/>
       </c>
     </row>
@@ -1653,7 +1664,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,14,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản mặt cầu*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 14, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Bản*")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n">
@@ -1682,8 +1693,8 @@
         <f>F18*1.208</f>
         <v/>
       </c>
-      <c r="L18" s="11">
-        <f>(J18/I18)*100</f>
+      <c r="L18" s="99">
+        <f>IF(I18=0, 0, (J18/I18)*100)</f>
         <v/>
       </c>
     </row>
@@ -1702,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="7">
-        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản quá độ*")</f>
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Bản quá độ*")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n">
@@ -1731,8 +1742,8 @@
         <f>F19*1.578</f>
         <v/>
       </c>
-      <c r="L19" s="11">
-        <f>(J19/I19)*100</f>
+      <c r="L19" s="99">
+        <f>IF(I19=0, 0, (J19/I19)*100)</f>
         <v/>
       </c>
     </row>
@@ -1755,8 +1766,8 @@
         <f>SUM(K6:K19)</f>
         <v/>
       </c>
-      <c r="L20" s="15">
-        <f>AVERAGE(L6:L19)</f>
+      <c r="L20" s="100">
+        <f>IFERROR(AVERAGE(L6:L19), 0)</f>
         <v/>
       </c>
     </row>
@@ -4742,10 +4753,8 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A6" s="103" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -4781,10 +4790,8 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A7" s="103" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
@@ -4821,10 +4828,8 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A8" s="103" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -4860,10 +4865,8 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A9" s="103" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
@@ -4899,10 +4902,8 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A10" s="103" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -4939,10 +4940,8 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A11" s="103" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
@@ -4978,10 +4977,8 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A12" s="103" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -5018,10 +5015,8 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A13" s="103" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
@@ -5058,10 +5053,8 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A14" s="103" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -5098,10 +5091,8 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A15" s="103" t="n">
+        <v>10</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
@@ -5137,10 +5128,8 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A16" s="103" t="n">
+        <v>11</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -5177,10 +5166,8 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A17" s="103" t="n">
+        <v>12</v>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
@@ -5217,10 +5204,8 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A18" s="103" t="n">
+        <v>13</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -5257,10 +5242,8 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A19" s="103" t="n">
+        <v>14</v>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
@@ -5297,10 +5280,8 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A20" s="103" t="n">
+        <v>15</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -5337,10 +5318,8 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A21" s="103" t="n">
+        <v>16</v>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
@@ -5377,10 +5356,8 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A22" s="103" t="n">
+        <v>17</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -5417,10 +5394,8 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A23" s="103" t="n">
+        <v>18</v>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
@@ -5457,10 +5432,8 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A24" s="103" t="n">
+        <v>19</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -5497,10 +5470,8 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A25" s="103" t="n">
+        <v>20</v>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
@@ -5537,10 +5508,8 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A26" s="103" t="n">
+        <v>21</v>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
@@ -5577,10 +5546,8 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A27" s="103" t="n">
+        <v>22</v>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
@@ -5758,7 +5725,7 @@
         </is>
       </c>
       <c r="C19" s="63">
-        <f>VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 3, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 3, FALSE), VLOOKUP(TEXT(C2, "@"), HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 3, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -5769,7 +5736,7 @@
         </is>
       </c>
       <c r="C20" s="84">
-        <f>TEXT(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 4, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 5, FALSE)</f>
+        <f>TEXT(IFERROR(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 4, FALSE), VLOOKUP(TEXT(C2, "@"), HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 4, FALSE)), "#,##0.00") &amp; " " &amp; IFERROR(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 5, FALSE), VLOOKUP(TEXT(C2, "@"), HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 5, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -5780,7 +5747,7 @@
         </is>
       </c>
       <c r="C21" s="92">
-        <f>VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 6, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 6, FALSE), VLOOKUP(TEXT(C2, "@"), HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 6, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -5791,7 +5758,7 @@
         </is>
       </c>
       <c r="C22" s="92">
-        <f>"Bắt đầu: 08 giờ 30 phút - Kết thúc: 11 giờ 30 phút, ngày " &amp; TEXT(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 8, FALSE), "dd/mm/yyyy")</f>
+        <f>"Bắt đầu: 08 giờ 30 phút - Kết thúc: 11 giờ 30 phút, ngày " &amp; TEXT(IFERROR(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 8, FALSE), VLOOKUP(TEXT(C2, "@"), HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 8, FALSE)), "dd/mm/yyyy")</f>
         <v/>
       </c>
     </row>
@@ -6010,7 +5977,7 @@
         </is>
       </c>
       <c r="C12" s="63">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 2, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 2, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 2, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6021,7 +5988,7 @@
         </is>
       </c>
       <c r="C13" s="84">
-        <f>TEXT(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 7, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 6, FALSE)</f>
+        <f>TEXT(IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 7, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 7, FALSE)), "#,##0.00") &amp; " " &amp; IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 6, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 6, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +5999,7 @@
         </is>
       </c>
       <c r="C14" s="92">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 3, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 3, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 3, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6043,7 +6010,7 @@
         </is>
       </c>
       <c r="C15" s="92">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 4, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 4, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 4, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6054,7 +6021,7 @@
         </is>
       </c>
       <c r="C16" s="92">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 10, FALSE) &amp; " (Số tổ mẫu: " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 9, FALSE) &amp; " tổ)"</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 10, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 10, FALSE)) &amp; " (Số tổ mẫu: " &amp; IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 9, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 9, FALSE)) &amp; " tổ)"</f>
         <v/>
       </c>
     </row>
@@ -6065,7 +6032,7 @@
         </is>
       </c>
       <c r="C17" s="92">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 11, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 11, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 11, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6076,7 +6043,7 @@
         </is>
       </c>
       <c r="C18" s="84">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 12, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 12, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 12, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6225,7 +6192,7 @@
         </is>
       </c>
       <c r="C12" s="63">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 2, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 2, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 2, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6236,7 +6203,7 @@
         </is>
       </c>
       <c r="C13" s="84">
-        <f>TEXT(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 7, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 6, FALSE)</f>
+        <f>TEXT(IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 7, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 7, FALSE)), "#,##0.00") &amp; " " &amp; IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 6, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 6, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -6247,7 +6214,7 @@
         </is>
       </c>
       <c r="C14" s="84">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 9, FALSE) &amp; " tổ mẫu (" &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 10, FALSE) &amp; ")"</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 9, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 9, FALSE)) &amp; " tổ mẫu (" &amp; IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 10, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 10, FALSE)) &amp; ")"</f>
         <v/>
       </c>
     </row>
@@ -6258,7 +6225,7 @@
         </is>
       </c>
       <c r="C15" s="92">
-        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 3, FALSE)</f>
+        <f>IFERROR(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 3, FALSE), VLOOKUP(TEXT(C2, "@"), CAP_PHOI_1M3_VA_TAN_SUAT!$A$24:$L$52, 3, FALSE))</f>
         <v/>
       </c>
     </row>
@@ -39430,10 +39397,8 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A24" s="101" t="n">
+        <v>1</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
@@ -39488,10 +39453,8 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A25" s="102" t="n">
+        <v>2</v>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
@@ -39546,10 +39509,8 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A26" s="101" t="n">
+        <v>3</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -39604,10 +39565,8 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A27" s="102" t="n">
+        <v>4</v>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
@@ -39662,10 +39621,8 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A28" s="101" t="n">
+        <v>5</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
@@ -39720,10 +39677,8 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A29" s="102" t="n">
+        <v>6</v>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
@@ -39778,10 +39733,8 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A30" s="101" t="n">
+        <v>7</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
@@ -39836,10 +39789,8 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A31" s="102" t="n">
+        <v>8</v>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
@@ -39894,10 +39845,8 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A32" s="101" t="n">
+        <v>9</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
@@ -39952,10 +39901,8 @@
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A33" s="102" t="n">
+        <v>10</v>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
@@ -40010,10 +39957,8 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A34" s="101" t="n">
+        <v>11</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
@@ -40068,10 +40013,8 @@
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A35" s="102" t="n">
+        <v>12</v>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
@@ -40126,10 +40069,8 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A36" s="101" t="n">
+        <v>13</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
@@ -40184,10 +40125,8 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A37" s="102" t="n">
+        <v>14</v>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
@@ -40242,10 +40181,8 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A38" s="101" t="n">
+        <v>15</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
@@ -40300,10 +40237,8 @@
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A39" s="102" t="n">
+        <v>16</v>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
@@ -40358,10 +40293,8 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A40" s="101" t="n">
+        <v>17</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
@@ -40416,10 +40349,8 @@
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A41" s="102" t="n">
+        <v>18</v>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
@@ -40474,10 +40405,8 @@
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A42" s="101" t="n">
+        <v>19</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -40532,10 +40461,8 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A43" s="102" t="n">
+        <v>20</v>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
@@ -40590,10 +40517,8 @@
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A44" s="101" t="n">
+        <v>21</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
@@ -40648,10 +40573,8 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A45" s="102" t="n">
+        <v>22</v>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
@@ -40706,10 +40629,8 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A46" s="101" t="n">
+        <v>23</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
@@ -40764,10 +40685,8 @@
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A47" s="102" t="n">
+        <v>24</v>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
@@ -40822,10 +40741,8 @@
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A48" s="101" t="n">
+        <v>25</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
@@ -40880,10 +40797,8 @@
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A49" s="102" t="n">
+        <v>26</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
@@ -40938,10 +40853,8 @@
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A50" s="101" t="n">
+        <v>27</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
@@ -40995,10 +40908,8 @@
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A51" s="102" t="n">
+        <v>28</v>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
@@ -41052,10 +40963,8 @@
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A52" s="101" t="n">
+        <v>29</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
@@ -48934,7 +48843,7 @@
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
       <c r="F32" s="7">
-        <f>C32*0.20</f>
+        <f>F31*0.20</f>
         <v/>
       </c>
       <c r="G32" s="31" t="inlineStr">
@@ -48957,7 +48866,7 @@
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="7">
-        <f>C32*0.05</f>
+        <f>F31*0.05</f>
         <v/>
       </c>
       <c r="G33" s="31" t="inlineStr">
@@ -48980,7 +48889,7 @@
       <c r="D34" s="13" t="n"/>
       <c r="E34" s="13" t="n"/>
       <c r="F34" s="37">
-        <f>C32-C33-C34</f>
+        <f>F31-F32-F33</f>
         <v/>
       </c>
       <c r="G34" s="38" t="inlineStr">
